--- a/table.xlsx
+++ b/table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD660D9E-2AC8-4CB2-8EE3-344E41618D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C59483-003A-42FB-A09C-D610DC1E2DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
@@ -75,7 +75,8 @@
     <t>8(16:00)</t>
   </si>
   <si>
-    <t>동아리</t>
+    <t>물리실
+동아리</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -204,16 +205,16 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -557,7 +558,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2">
@@ -572,10 +573,10 @@
       <c r="E2" s="2">
         <v>203</v>
       </c>
-      <c r="F2" s="5"/>
+      <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8"/>
+      <c r="A3" s="6"/>
       <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
@@ -588,10 +589,10 @@
       <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2">
@@ -606,10 +607,10 @@
       <c r="E4" s="2">
         <v>203</v>
       </c>
-      <c r="F4" s="5"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="8"/>
+      <c r="A5" s="6"/>
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
@@ -622,37 +623,37 @@
       <c r="E5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="2">
         <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="8"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
       <c r="E8" s="2">
         <v>107</v>
       </c>
@@ -661,10 +662,10 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
       <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
@@ -673,7 +674,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="2">
@@ -685,13 +686,13 @@
       <c r="D10" s="2">
         <v>206</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="8"/>
+      <c r="A11" s="6"/>
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
@@ -701,11 +702,11 @@
       <c r="D11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="2">
@@ -717,13 +718,13 @@
       <c r="D12" s="2">
         <v>206</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="8"/>
+      <c r="A13" s="6"/>
       <c r="B13" s="3" t="s">
         <v>7</v>
       </c>
@@ -733,8 +734,8 @@
       <c r="D13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
@@ -758,15 +759,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="E12:E13"/>
@@ -777,6 +769,15 @@
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table.xlsx
+++ b/table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C59483-003A-42FB-A09C-D610DC1E2DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD4DF9E-F7BC-4BC7-8326-DAC43D1B05CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
   <si>
     <t>교시</t>
   </si>
@@ -48,9 +48,6 @@
     <t>1(08:20)</t>
   </si>
   <si>
-    <t>역학</t>
-  </si>
-  <si>
     <t>2(09:20)</t>
   </si>
   <si>
@@ -60,9 +57,6 @@
     <t>4(11:20)</t>
   </si>
   <si>
-    <t>통과A</t>
-  </si>
-  <si>
     <t>5(13:00)</t>
   </si>
   <si>
@@ -75,9 +69,17 @@
     <t>8(16:00)</t>
   </si>
   <si>
-    <t>물리실
-동아리</t>
+    <t>동아리</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>생II</t>
+  </si>
+  <si>
+    <t>과실2</t>
+  </si>
+  <si>
+    <t>근면</t>
   </si>
 </sst>
 </file>
@@ -561,185 +563,185 @@
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2">
-        <v>206</v>
-      </c>
+      <c r="B2" s="7"/>
       <c r="C2" s="2">
-        <v>201</v>
+        <v>301</v>
       </c>
       <c r="D2" s="2">
-        <v>205</v>
+        <v>102</v>
       </c>
       <c r="E2" s="2">
-        <v>203</v>
+        <v>301</v>
       </c>
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="B3" s="8"/>
       <c r="C3" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2">
-        <v>206</v>
+        <v>105</v>
       </c>
       <c r="C4" s="2">
-        <v>201</v>
+        <v>302</v>
       </c>
       <c r="D4" s="2">
-        <v>205</v>
-      </c>
-      <c r="E4" s="2">
-        <v>203</v>
-      </c>
-      <c r="F4" s="7"/>
+        <v>103</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="2">
+        <v>104</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
       <c r="B5" s="3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7"/>
+        <v>8</v>
+      </c>
+      <c r="B6" s="2">
+        <v>303</v>
+      </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="2">
-        <v>201</v>
-      </c>
+      <c r="E6" s="2">
+        <v>309</v>
+      </c>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
-      <c r="B7" s="8"/>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="C8" s="2">
+        <v>303</v>
+      </c>
+      <c r="D8" s="2">
+        <v>101</v>
+      </c>
       <c r="E8" s="2">
-        <v>107</v>
+        <v>309</v>
       </c>
       <c r="F8" s="2">
-        <v>201</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="C9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E9" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2">
-        <v>205</v>
-      </c>
-      <c r="C10" s="2">
-        <v>203</v>
-      </c>
-      <c r="D10" s="2">
-        <v>206</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
       <c r="B11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>205</v>
-      </c>
-      <c r="C12" s="2">
-        <v>203</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="C12" s="7"/>
       <c r="D12" s="2">
-        <v>206</v>
-      </c>
-      <c r="E12" s="7"/>
+        <v>303</v>
+      </c>
+      <c r="E12" s="2">
+        <v>106</v>
+      </c>
       <c r="F12" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
       <c r="B13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>7</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C13" s="8"/>
       <c r="D13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="8"/>
+        <v>17</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -749,7 +751,7 @@
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -761,23 +763,23 @@
   <mergeCells count="19">
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="E12:E13"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="E10:E11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:F5"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table.xlsx
+++ b/table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD4DF9E-F7BC-4BC7-8326-DAC43D1B05CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B713D5D-D366-465A-89EB-F10F4873C16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
   <si>
     <t>교시</t>
   </si>
@@ -48,6 +48,9 @@
     <t>1(08:20)</t>
   </si>
   <si>
+    <t>역학</t>
+  </si>
+  <si>
     <t>2(09:20)</t>
   </si>
   <si>
@@ -55,6 +58,9 @@
   </si>
   <si>
     <t>4(11:20)</t>
+  </si>
+  <si>
+    <t>통과A</t>
   </si>
   <si>
     <t>5(13:00)</t>
@@ -71,15 +77,6 @@
   <si>
     <t>동아리</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>생II</t>
-  </si>
-  <si>
-    <t>과실2</t>
-  </si>
-  <si>
-    <t>근면</t>
   </si>
 </sst>
 </file>
@@ -207,6 +204,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -214,12 +217,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -560,188 +557,188 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="2">
+        <v>206</v>
+      </c>
       <c r="C2" s="2">
-        <v>301</v>
+        <v>201</v>
       </c>
       <c r="D2" s="2">
-        <v>102</v>
+        <v>205</v>
       </c>
       <c r="E2" s="2">
-        <v>301</v>
-      </c>
-      <c r="F2" s="7"/>
+        <v>203</v>
+      </c>
+      <c r="F2" s="9"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="C3" s="3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2">
+        <v>206</v>
+      </c>
+      <c r="C4" s="2">
+        <v>201</v>
+      </c>
+      <c r="D4" s="2">
+        <v>205</v>
+      </c>
+      <c r="E4" s="2">
+        <v>203</v>
+      </c>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="8"/>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="8"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="2">
+        <v>107</v>
+      </c>
+      <c r="F8" s="2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="8"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2">
+        <v>205</v>
+      </c>
+      <c r="C10" s="2">
+        <v>203</v>
+      </c>
+      <c r="D10" s="2">
+        <v>206</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="8"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2">
-        <v>105</v>
-      </c>
-      <c r="C4" s="2">
-        <v>302</v>
-      </c>
-      <c r="D4" s="2">
-        <v>103</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="2">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="8"/>
+      <c r="B11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2">
+        <v>205</v>
+      </c>
+      <c r="C12" s="2">
+        <v>203</v>
+      </c>
+      <c r="D12" s="2">
+        <v>206</v>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2">
-        <v>303</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="2">
-        <v>309</v>
-      </c>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6"/>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="2">
-        <v>303</v>
-      </c>
-      <c r="D8" s="2">
-        <v>101</v>
-      </c>
-      <c r="E8" s="2">
-        <v>309</v>
-      </c>
-      <c r="F8" s="2">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="2">
-        <v>307</v>
-      </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6"/>
-      <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2">
-        <v>307</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="2">
-        <v>303</v>
-      </c>
-      <c r="E12" s="2">
-        <v>106</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6"/>
+      <c r="A13" s="8"/>
       <c r="B13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="8"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="D13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="8"/>
+        <v>7</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -751,7 +748,7 @@
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -761,25 +758,25 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="E12:E13"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
